--- a/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD6D1E8-B20F-4626-8698-65628B625B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95463837-F8CB-42A3-9DD3-4543A348B168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>WHAT TO CHECK</t>
   </si>
@@ -52,6 +52,27 @@
   </si>
   <si>
     <t>a dashboard to test the model exists</t>
+  </si>
+  <si>
+    <t>correct imputation has been implemented and not just dropna</t>
+  </si>
+  <si>
+    <t>have you set seed for models that may not be reproducible</t>
+  </si>
+  <si>
+    <t>bias in history/date/year</t>
+  </si>
+  <si>
+    <t>bias in demography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fit scalar on the training data then transform on test and train </t>
+  </si>
+  <si>
+    <t>Transformation -&gt; Train-Test -&gt; preprocess for imputation -&gt; Imputation -&gt; After imputation -&gt; Preprocess for model -&gt; Model training -&gt; after model training</t>
+  </si>
+  <si>
+    <t>imputation was done without including the y column/label in the classification data</t>
   </si>
 </sst>
 </file>
@@ -96,7 +117,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -107,6 +132,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CA5B914-5B14-479B-9857-9597D5ABFEF8}" name="Table1" displayName="Table1" ref="A1:B1048576" totalsRowShown="0">
+  <autoFilter ref="A1:B1048576" xr:uid="{4CA5B914-5B14-479B-9857-9597D5ABFEF8}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{ECD4E069-EF52-4EC3-B4C8-C91D84EBC041}" name="WHAT TO CHECK" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{9A73668F-9B0F-4E4E-A66F-DD205AB47EEE}" name="DONE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -372,10 +408,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.7265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="65.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -421,7 +457,45 @@
         <v>8</v>
       </c>
     </row>
+    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95463837-F8CB-42A3-9DD3-4543A348B168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D84E5F-DE2E-4604-AEEC-9966C12DD531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>WHAT TO CHECK</t>
   </si>
@@ -73,6 +73,54 @@
   </si>
   <si>
     <t>imputation was done without including the y column/label in the classification data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">do you have a predict function </t>
+  </si>
+  <si>
+    <t>Train-test split has been performed correctly.</t>
+  </si>
+  <si>
+    <t>No data leakage: imputation and preprocessing are done without using the target variable (y).</t>
+  </si>
+  <si>
+    <t>Scaling is fit on the training data only and then applied to both train and test sets.</t>
+  </si>
+  <si>
+    <t>A clear pipeline is followed from transformation to train-test split, preprocessing for imputation, imputation, post-imputation preprocessing, model training, and post-training steps.</t>
+  </si>
+  <si>
+    <t>Imputation is implemented appropriately and not just using dropna.</t>
+  </si>
+  <si>
+    <t>Upsampling or resampling is applied only on the training set and not on the test set.</t>
+  </si>
+  <si>
+    <t>For imbalanced test data, appropriate evaluation metrics such as F1-score and MCC are used.</t>
+  </si>
+  <si>
+    <t>K-fold cross-validation has been performed.</t>
+  </si>
+  <si>
+    <t>Random seeds are set for models to ensure reproducibility.</t>
+  </si>
+  <si>
+    <t>Potential bias in time-related features such as history, date, or year has been assessed.</t>
+  </si>
+  <si>
+    <t>Potential bias in demographic variables has been evaluated.</t>
+  </si>
+  <si>
+    <t>A predict function is implemented and usable.</t>
+  </si>
+  <si>
+    <t>A dashboard or interface exists for testing the model.</t>
+  </si>
+  <si>
+    <t>A mechanism exists to monitor model performance over time.</t>
+  </si>
+  <si>
+    <t>A process is in place to update or retrain the model when necessary.</t>
   </si>
 </sst>
 </file>
@@ -408,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.7265625" style="1" customWidth="1"/>
@@ -427,12 +475,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -442,12 +490,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -457,12 +505,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -490,6 +538,86 @@
     <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D84E5F-DE2E-4604-AEEC-9966C12DD531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1E0B36-800F-44AB-9CAF-A55047955176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>WHAT TO CHECK</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>A process is in place to update or retrain the model when necessary.</t>
+  </si>
+  <si>
+    <t>You have logged the count of the following:
+1. the rows of data
+2. the number of each class
+3. the number of missing rows for each column</t>
   </si>
 </sst>
 </file>
@@ -545,6 +551,11 @@
         <v>16</v>
       </c>
     </row>
+    <row r="17" spans="1:1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>17</v>

--- a/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1E0B36-800F-44AB-9CAF-A55047955176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D788CDD0-2A10-4D52-8C96-DACE70E40586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>WHAT TO CHECK</t>
   </si>
@@ -127,6 +127,12 @@
 1. the rows of data
 2. the number of each class
 3. the number of missing rows for each column</t>
+  </si>
+  <si>
+    <t>Ensure you have a stable training data that has been critiqued by the stakeholder</t>
+  </si>
+  <si>
+    <t>imputation training was done only on the training dataset</t>
   </si>
 </sst>
 </file>
@@ -556,6 +562,16 @@
         <v>32</v>
       </c>
     </row>
+    <row r="18" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>17</v>

--- a/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D788CDD0-2A10-4D52-8C96-DACE70E40586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5343AE2-EC64-4F5A-8661-D6EFF3372C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>WHAT TO CHECK</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>imputation training was done only on the training dataset</t>
+  </si>
+  <si>
+    <t>Ensure Brier score has been computed as part of the evaluation</t>
   </si>
 </sst>
 </file>
@@ -572,6 +575,11 @@
         <v>34</v>
       </c>
     </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>17</v>

--- a/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
+++ b/dspackagefolder/template/checklist/ML_CHECKLIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajim\Desktop\NonPHD_Muizdeen\INTERVIEWS\dspackage\dspackagefolder\template\checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5343AE2-EC64-4F5A-8661-D6EFF3372C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98867634-3111-439A-B3ED-12740A6F716B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>WHAT TO CHECK</t>
   </si>
@@ -33,122 +33,162 @@
     <t>DONE</t>
   </si>
   <si>
-    <t>train test split has been done</t>
-  </si>
-  <si>
-    <t>data upsampled on the train but not on the test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if test data is imbalanced, has f1, mcc been used for evaluation. </t>
-  </si>
-  <si>
-    <t>K-fold cross validation has been done</t>
-  </si>
-  <si>
-    <t>a mechanism to monitor the model performance exists</t>
-  </si>
-  <si>
-    <t>a mechanism to update the model when needed</t>
-  </si>
-  <si>
-    <t>a dashboard to test the model exists</t>
-  </si>
-  <si>
-    <t>correct imputation has been implemented and not just dropna</t>
-  </si>
-  <si>
-    <t>have you set seed for models that may not be reproducible</t>
-  </si>
-  <si>
-    <t>bias in history/date/year</t>
-  </si>
-  <si>
-    <t>bias in demography</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fit scalar on the training data then transform on test and train </t>
-  </si>
-  <si>
-    <t>Transformation -&gt; Train-Test -&gt; preprocess for imputation -&gt; Imputation -&gt; After imputation -&gt; Preprocess for model -&gt; Model training -&gt; after model training</t>
-  </si>
-  <si>
-    <t>imputation was done without including the y column/label in the classification data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">do you have a predict function </t>
-  </si>
-  <si>
-    <t>Train-test split has been performed correctly.</t>
-  </si>
-  <si>
-    <t>No data leakage: imputation and preprocessing are done without using the target variable (y).</t>
-  </si>
-  <si>
-    <t>Scaling is fit on the training data only and then applied to both train and test sets.</t>
-  </si>
-  <si>
-    <t>A clear pipeline is followed from transformation to train-test split, preprocessing for imputation, imputation, post-imputation preprocessing, model training, and post-training steps.</t>
-  </si>
-  <si>
-    <t>Imputation is implemented appropriately and not just using dropna.</t>
-  </si>
-  <si>
-    <t>Upsampling or resampling is applied only on the training set and not on the test set.</t>
-  </si>
-  <si>
-    <t>For imbalanced test data, appropriate evaluation metrics such as F1-score and MCC are used.</t>
-  </si>
-  <si>
-    <t>K-fold cross-validation has been performed.</t>
-  </si>
-  <si>
-    <t>Random seeds are set for models to ensure reproducibility.</t>
-  </si>
-  <si>
-    <t>Potential bias in time-related features such as history, date, or year has been assessed.</t>
-  </si>
-  <si>
-    <t>Potential bias in demographic variables has been evaluated.</t>
-  </si>
-  <si>
-    <t>A predict function is implemented and usable.</t>
-  </si>
-  <si>
-    <t>A dashboard or interface exists for testing the model.</t>
-  </si>
-  <si>
-    <t>A mechanism exists to monitor model performance over time.</t>
-  </si>
-  <si>
-    <t>A process is in place to update or retrain the model when necessary.</t>
-  </si>
-  <si>
-    <t>You have logged the count of the following:
-1. the rows of data
-2. the number of each class
-3. the number of missing rows for each column</t>
-  </si>
-  <si>
-    <t>Ensure you have a stable training data that has been critiqued by the stakeholder</t>
-  </si>
-  <si>
-    <t>imputation training was done only on the training dataset</t>
-  </si>
-  <si>
-    <t>Ensure Brier score has been computed as part of the evaluation</t>
+    <t>Machine Learning Checklist</t>
+  </si>
+  <si>
+    <t>Ensure the training dataset is stable and has been reviewed and critiqued by stakeholders.</t>
+  </si>
+  <si>
+    <t>Ensure the training dataset has been quality assured in at least 10 different ways.</t>
+  </si>
+  <si>
+    <t>Log the total number of rows, class distribution, and missing values for each column.</t>
+  </si>
+  <si>
+    <t>Assess potential bias in historical, date, and time-related features.</t>
+  </si>
+  <si>
+    <t>Assess potential bias in demographic features.</t>
+  </si>
+  <si>
+    <t>Set random seeds for all non-deterministic processes to ensure reproducibility.</t>
+  </si>
+  <si>
+    <t>Perform the train-test split correctly before fitting any preprocessing or modelling components.</t>
+  </si>
+  <si>
+    <t>Ensure there is no data leakage throughout the pipeline.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement an appropriate imputation strategy rather than simply using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dropna()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exclude the target variable (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) when fitting imputation models in supervised learning tasks.</t>
+    </r>
+  </si>
+  <si>
+    <t>Fit imputation models using only the training data and apply them to both the training and test datasets.</t>
+  </si>
+  <si>
+    <t>Fit scalers and other preprocessing transformations on the training data only and apply them to both the training and test datasets.</t>
+  </si>
+  <si>
+    <t>Follow a well-defined pipeline: transformations → train-test split → preprocessing for imputation → imputation → post-imputation preprocessing → model training → post-training evaluation.</t>
+  </si>
+  <si>
+    <t>Apply upsampling or resampling only to the training data and never to the test data.</t>
+  </si>
+  <si>
+    <t>Perform K-fold cross-validation on the training dataset.</t>
+  </si>
+  <si>
+    <t>Use appropriate evaluation metrics for imbalanced classification problems, including F1-score and Matthews Correlation Coefficient (MCC).</t>
+  </si>
+  <si>
+    <t>Compute the Brier score when evaluating models that produce probability estimates.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement and validate a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>predict()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> function for inference on new data.</t>
+    </r>
+  </si>
+  <si>
+    <t>Provide a dashboard or interface for testing and interacting with the model.</t>
+  </si>
+  <si>
+    <t>Implement a mechanism to monitor model performance in production.</t>
+  </si>
+  <si>
+    <t>Implement a process to retrain or update the model when performance deteriorates or data changes.</t>
+  </si>
+  <si>
+    <t>categorical columns have been made one-hot encoding</t>
+  </si>
+  <si>
+    <t>assumptions are listed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -171,10 +211,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -198,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CA5B914-5B14-479B-9857-9597D5ABFEF8}" name="Table1" displayName="Table1" ref="A1:B1048576" totalsRowShown="0">
-  <autoFilter ref="A1:B1048576" xr:uid="{4CA5B914-5B14-479B-9857-9597D5ABFEF8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CA5B914-5B14-479B-9857-9597D5ABFEF8}" name="Table1" displayName="Table1" ref="A1:B1048532" totalsRowShown="0">
+  <autoFilter ref="A1:B1048532" xr:uid="{4CA5B914-5B14-479B-9857-9597D5ABFEF8}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{ECD4E069-EF52-4EC3-B4C8-C91D84EBC041}" name="WHAT TO CHECK" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{9A73668F-9B0F-4E4E-A66F-DD205AB47EEE}" name="DONE"/>
@@ -471,13 +517,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="65.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,174 +531,187 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2" ht="23.5">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" ht="29">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" spans="1:2" ht="29">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:2" ht="29">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:2" ht="29">
+      <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:2" ht="29">
+      <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="3"/>
+    </row>
+    <row r="20" spans="1:1" ht="29">
+      <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" ht="29">
+      <c r="A22" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:1" ht="29">
+      <c r="A24" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:1" ht="29">
+      <c r="A26" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="3"/>
+    </row>
+    <row r="28" spans="1:1" ht="43.5">
+      <c r="A28" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="3"/>
+    </row>
+    <row r="30" spans="1:1" ht="29">
+      <c r="A30" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="3"/>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:1">
+      <c r="A33" s="3"/>
+    </row>
+    <row r="34" spans="1:1" ht="29">
+      <c r="A34" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:1" ht="29">
+      <c r="A36" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+    <row r="41" spans="1:1">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:1" ht="29">
+      <c r="A44" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
